--- a/examples/ausl_2027.xlsx
+++ b/examples/ausl_2027.xlsx
@@ -1361,12 +1361,15 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Hard</t>
-        </is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>100</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Only Chicago hosts 7/11-15 (All-Star Weekend travel)</t>
+          <t>Only Chicago hosts 7/11-15 (All-Star Weekend travel). Soft because it conflicts with R10 (Round Rock must host 7/15); as Hard there is no valid schedule</t>
         </is>
       </c>
     </row>

--- a/examples/ausl_2027.xlsx
+++ b/examples/ausl_2027.xlsx
@@ -5607,7 +5607,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Teams, Opponents, Dates, Min, Max, N</t>
+          <t>Teams, Opponents, Min, Max, N</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>game beyond Max; block shorter than Min; gap longer than N</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Minimum days between the end of one block against an opponent and the start of the next block against the same opponent.</t>
+          <t>Minimum days from the last game of one block against an opponent to the first game of the next block against the same opponent (e.g. last game 7/1, N = 14: next block starts 7/15 or later).</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Minimum off days between a team's last game against one opponent and its next game against a different opponent.</t>
+          <t>Minimum off days between a team's last game against one opponent and its next game against a different opponent. Dates/Days filter the day of the next game.</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Minimum off days when a team moves between locations, for moves from a From location to a To location. Every game is at the home team's location, so locations are hosting team codes, or any / home / away (home = the team's own home games).</t>
+          <t>Minimum off days when a team moves between locations, for moves from a From location to a different To location. Every game is at the home team's location, so locations are hosting team codes, or any / home / away (home = the team's own home games). Dates/Days filter the day of the game moved to.</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>When a team leaves a From location for a different location, its next location should be a To location.</t>
+          <t>When a team leaves a From location for a different location, its next location should be a To location. Role = away applies when the team was visiting the From location; Role = home when it was playing at home.</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Limits the length of a homestand (Role = home) or road trip (Role = away). Option = games counts consecutive games; days counts calendar days from first to last game of the run.</t>
+          <t>Limits the length of a homestand (Role = home) or road trip (Role = away). Option = games counts consecutive games; days counts calendar days from the first to the last game of the run, inclusive. Off days don't break a run.</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>game beyond the limit</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Number of games a team plays per window. Option = rolling checks every N-day window; week checks each Mon-Sun calendar week.</t>
+          <t>Number of games a team plays per window. Option = rolling checks every N-day window; week checks each Mon-Sun calendar week. Dates/Days limit which games are counted. Min applies only to windows that lie entirely inside the season.</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">

--- a/examples/ausl_2027.xlsx
+++ b/examples/ausl_2027.xlsx
@@ -5124,6 +5124,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -5251,6 +5252,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -5306,6 +5308,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>

--- a/examples/ausl_2027.xlsx
+++ b/examples/ausl_2027.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Optional: a previous run folder to compare against / minimize changes from</t>
+          <t>Optional: a previous schedule workbook (from wildflyer solve) to build from and compare against, e.g. schedule_v3.xlsx (relative to this file's folder)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Optional: soft cost for each game that differs from the base run (0 = off)</t>
+          <t>Optional: soft cost for each base-run game that is moved or dropped (blank/0 = off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lock base before</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Optional: freeze the schedule before this date exactly as in the base run (same games, none added)</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5889,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Favour (Option = prefer) or discourage (Option = avoid) games on matching dates. Each matching game earns or costs Weight. Teams/Role narrow which games count. Soft only.</t>
+          <t>Favour (Option = prefer) or discourage (Option = avoid) games on matching dates/days. prefer: each game NOT on the listed dates/days costs Weight; avoid: each game ON them costs Weight. Teams/Role narrow which games count (Role = home: games the Teams host); each game is counted once. Soft only.</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -5897,7 +5909,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>game</t>
+          <t>game outside / inside the dates</t>
         </is>
       </c>
     </row>

--- a/examples/ausl_2027.xlsx
+++ b/examples/ausl_2027.xlsx
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>A run of a team's games against one opponent with no game against anyone else in between. Off days do not break a block.</t>
+          <t>A series: a run of a team's games against one opponent at one location, with no other game in between. Off days do not break a block; a change of location does.</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Games against the same opponent come in blocks. A block is a run of a team's games against one opponent with no game against anyone else in between (off days don't break a block). Min/Max = games per block; N = most off days allowed between consecutive games inside a block.</t>
+          <t>Games against the same opponent come in blocks (series). A block is a run of a team's games against one opponent at one location, with no other game in between. Off days don't break a block; a change of location does (home games and away games against the same opponent are separate blocks). Min/Max = games per block; N = most off days allowed between consecutive games inside a block.</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
